--- a/Capacity by Plant.xlsx
+++ b/Capacity by Plant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZachF\Desktop\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953B22BF-7848-44A0-A143-EE538F9A3847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD4B4F6-30B3-463F-A702-9308F59ABE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C7A1581-7433-4ABA-BE68-43C5F4B97E1B}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{4C7A1581-7433-4ABA-BE68-43C5F4B97E1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Task" sheetId="1" r:id="rId1"/>
@@ -328,6 +328,52 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Task!$C$6:$N$7</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Sep
+FY26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Dec</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Jul
+FY27</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Aug</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Task!$C$8:$N$8</c:f>
@@ -409,6 +455,52 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Task!$C$6:$N$7</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Sep
+FY26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Dec</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Jul
+FY27</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Aug</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Task!$C$10:$N$10</c:f>
@@ -490,6 +582,52 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Task!$C$6:$N$7</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Sep
+FY26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Dec</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Jul
+FY27</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Aug</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Task!$C$12:$N$12</c:f>
@@ -827,6 +965,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
